--- a/target/test-classes/testData/RestAPI_testData.xlsx
+++ b/target/test-classes/testData/RestAPI_testData.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tania\October21_Selenium\NNRestAssuredAPI\src\test\java\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129D18F0-CA3A-41E3-9E6C-728B1C7EAD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA431C47-3606-4CF5-BB86-4D27C26D9142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11496" yWindow="1116" windowWidth="11892" windowHeight="8496" xr2:uid="{1DE825DB-DD12-4207-8A44-137B225D8646}"/>
+    <workbookView xWindow="10500" yWindow="2028" windowWidth="11892" windowHeight="8496" activeTab="2" xr2:uid="{1DE825DB-DD12-4207-8A44-137B225D8646}"/>
   </bookViews>
   <sheets>
     <sheet name="UserAPI" sheetId="1" r:id="rId1"/>
+    <sheet name="SkillAPI" sheetId="2" r:id="rId2"/>
+    <sheet name="UserSkillMapAPI" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>comments</t>
   </si>
@@ -86,6 +88,24 @@
   </si>
   <si>
     <t>John,Jonas</t>
+  </si>
+  <si>
+    <t>skill_name</t>
+  </si>
+  <si>
+    <t>SDET 70</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>months_of_exp</t>
+  </si>
+  <si>
+    <t>U1</t>
   </si>
 </sst>
 </file>
@@ -551,4 +571,63 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5790691-7A2C-46AB-BAF4-19CA5964CD3F}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F910293-75DD-48F7-9E42-22755EF2AE7F}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>